--- a/PythonProject/results/Confronto Metriche.xlsx
+++ b/PythonProject/results/Confronto Metriche.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_789\Desktop\Sviluppo\ML_4_VIsion_-_Multimedia\PythonProject\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62F3C50-8F94-4852-AEE2-05D699FEFECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29B1A71-9B4D-4925-AC84-35F0CD0C3E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,7 +378,7 @@
     <t>0.1342597673397718</t>
   </si>
   <si>
-    <t>Dataset - M05_E40_LR00025</t>
+    <t>Dataset - M04_E40_LR00025</t>
   </si>
 </sst>
 </file>
@@ -696,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XFD28"/>
+  <dimension ref="A1:XFD33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.81640625" customWidth="1"/>
@@ -706,8 +706,8 @@
     <col min="5" max="5" width="18.7265625" customWidth="1"/>
     <col min="6" max="6" width="19.90625" customWidth="1"/>
     <col min="7" max="7" width="19.26953125" customWidth="1"/>
-    <col min="8" max="8" width="18.54296875" customWidth="1"/>
-    <col min="9" max="9" width="19.1796875" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" customWidth="1"/>
+    <col min="9" max="9" width="21.36328125" customWidth="1"/>
     <col min="10" max="10" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -897,99 +897,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>7</v>
-      </c>
-      <c r="J11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" t="s">
-        <v>70</v>
-      </c>
-      <c r="J13" t="s">
-        <v>71</v>
-      </c>
-    </row>
+    <row r="11" spans="1:10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:10" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>117</v>
@@ -99499,6 +99409,99 @@
       </c>
       <c r="J28" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" t="s">
+        <v>7</v>
+      </c>
+      <c r="J31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16384" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" t="s">
+        <v>63</v>
+      </c>
+      <c r="J32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" t="s">
+        <v>70</v>
+      </c>
+      <c r="J33" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/PythonProject/results/Confronto Metriche.xlsx
+++ b/PythonProject/results/Confronto Metriche.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_789\Desktop\Sviluppo\ML_4_VIsion_-_Multimedia\PythonProject\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60112102-8C28-4D36-B6C4-F2A9EDA4962E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44A878D-E151-4F2A-BA85-5FC786395EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
   <si>
     <t>Loss</t>
   </si>
@@ -118,6 +118,60 @@
   </si>
   <si>
     <t>Queries_Tot</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Queries_Total</t>
+  </si>
+  <si>
+    <t>0.11701907452049626</t>
+  </si>
+  <si>
+    <t>0.4587856302165331</t>
+  </si>
+  <si>
+    <t>0.8988880467988666</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>0.7566666666666668</t>
+  </si>
+  <si>
+    <t>0.6773333333333331</t>
+  </si>
+  <si>
+    <t>0.03079448766575302</t>
+  </si>
+  <si>
+    <t>0.12192250291096936</t>
+  </si>
+  <si>
+    <t>0.19973161640125187</t>
+  </si>
+  <si>
+    <t>0.5756013733734875</t>
+  </si>
+  <si>
+    <t>0.8800223214285714</t>
+  </si>
+  <si>
+    <t>0.8125</t>
+  </si>
+  <si>
+    <t>0.771875</t>
+  </si>
+  <si>
+    <t>0.01179554195136848</t>
+  </si>
+  <si>
+    <t>0.05895772893842809</t>
+  </si>
+  <si>
+    <t>0.11201445617182634</t>
   </si>
 </sst>
 </file>
@@ -435,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.81640625" customWidth="1"/>
@@ -563,6 +617,117 @@
         <v>32</v>
       </c>
     </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7">
+        <v>300</v>
+      </c>
+      <c r="L7">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8">
+        <v>32</v>
+      </c>
+      <c r="L8">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PythonProject/results/Confronto Metriche.xlsx
+++ b/PythonProject/results/Confronto Metriche.xlsx
@@ -1,31 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_789\Desktop\Sviluppo\ML_4_VIsion_-_Multimedia\PythonProject\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44A878D-E151-4F2A-BA85-5FC786395EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527FB495-020D-4798-A97D-550E13AE8CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="90">
+  <si>
+    <t>Dataset - M04 - E10 - LR000025</t>
+  </si>
   <si>
     <t>Loss</t>
   </si>
@@ -54,51 +52,57 @@
     <t>Recall@10</t>
   </si>
   <si>
+    <t>Queries_Tot</t>
+  </si>
+  <si>
+    <t>Queries_Used</t>
+  </si>
+  <si>
     <t>LogoDet-3K</t>
   </si>
   <si>
+    <t>0.08284072020747593</t>
+  </si>
+  <si>
+    <t>0.49184648521911406</t>
+  </si>
+  <si>
+    <t>0.9209890555255942</t>
+  </si>
+  <si>
+    <t>0.9033333333333333</t>
+  </si>
+  <si>
+    <t>0.7946666666666666</t>
+  </si>
+  <si>
+    <t>0.7126666666666669</t>
+  </si>
+  <si>
+    <t>0.033715400576027954</t>
+  </si>
+  <si>
+    <t>0.13439874637739718</t>
+  </si>
+  <si>
+    <t>0.21642333001153957</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
     <t>FlickrLogos-32</t>
   </si>
   <si>
+    <t>0.56585494407234</t>
+  </si>
+  <si>
+    <t>0.9291666666666666</t>
+  </si>
+  <si>
     <t>0.90625</t>
   </si>
   <si>
-    <t>Queries_Used</t>
-  </si>
-  <si>
-    <t>0.08284072020747593</t>
-  </si>
-  <si>
-    <t>0.49184648521911406</t>
-  </si>
-  <si>
-    <t>0.9209890555255942</t>
-  </si>
-  <si>
-    <t>0.9033333333333333</t>
-  </si>
-  <si>
-    <t>0.7946666666666666</t>
-  </si>
-  <si>
-    <t>0.7126666666666669</t>
-  </si>
-  <si>
-    <t>0.033715400576027954</t>
-  </si>
-  <si>
-    <t>0.13439874637739718</t>
-  </si>
-  <si>
-    <t>0.21642333001153957</t>
-  </si>
-  <si>
-    <t>0.56585494407234</t>
-  </si>
-  <si>
-    <t>0.9291666666666666</t>
-  </si>
-  <si>
     <t>0.8062500000000001</t>
   </si>
   <si>
@@ -114,10 +118,7 @@
     <t>0.10930372514028328</t>
   </si>
   <si>
-    <t>Dataset - M04 - E10 - LR000025</t>
-  </si>
-  <si>
-    <t>Queries_Tot</t>
+    <t>32</t>
   </si>
   <si>
     <t>Dataset</t>
@@ -172,6 +173,123 @@
   </si>
   <si>
     <t>0.11201445617182634</t>
+  </si>
+  <si>
+    <t>Dataset - M05 - E5 - LR00001</t>
+  </si>
+  <si>
+    <t>Queries_Used_x000D_</t>
+  </si>
+  <si>
+    <t>0.07836746598244687</t>
+  </si>
+  <si>
+    <t>0.6262976233621287</t>
+  </si>
+  <si>
+    <t>0.9423789772899043</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>0.8580000000000001</t>
+  </si>
+  <si>
+    <t>0.7913333333333337</t>
+  </si>
+  <si>
+    <t>0.035170633922716285</t>
+  </si>
+  <si>
+    <t>0.14736630005371554</t>
+  </si>
+  <si>
+    <t>0.24331679791316052</t>
+  </si>
+  <si>
+    <t>300_x000D_</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0.7502549395891813</t>
+  </si>
+  <si>
+    <t>0.9391369047619048</t>
+  </si>
+  <si>
+    <t>0.9375</t>
+  </si>
+  <si>
+    <t>0.9125</t>
+  </si>
+  <si>
+    <t>0.915625</t>
+  </si>
+  <si>
+    <t>0.013600475881462258</t>
+  </si>
+  <si>
+    <t>0.06619078520441275</t>
+  </si>
+  <si>
+    <t>0.13283446895955012</t>
+  </si>
+  <si>
+    <t>Dataset - M04 - E15 - LR Decay Aug</t>
+  </si>
+  <si>
+    <t>0.05701762896243463</t>
+  </si>
+  <si>
+    <t>0.6016630060846416</t>
+  </si>
+  <si>
+    <t>0.928498085396956</t>
+  </si>
+  <si>
+    <t>0.9173553719008265</t>
+  </si>
+  <si>
+    <t>0.8132231404958679</t>
+  </si>
+  <si>
+    <t>0.7545454545454545</t>
+  </si>
+  <si>
+    <t>0.035392343620477815</t>
+  </si>
+  <si>
+    <t>0.14106921658622504</t>
+  </si>
+  <si>
+    <t>0.24943371034300452</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>121_x000D_</t>
+  </si>
+  <si>
+    <t>0.7161635578236768</t>
+  </si>
+  <si>
+    <t>0.9427083333333333</t>
+  </si>
+  <si>
+    <t>0.9062499999999999</t>
+  </si>
+  <si>
+    <t>0.88125</t>
+  </si>
+  <si>
+    <t>0.06576452774490721</t>
+  </si>
+  <si>
+    <t>0.12789254653840776</t>
   </si>
 </sst>
 </file>
@@ -180,7 +298,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -214,7 +332,7 @@
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -237,44 +355,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -304,12 +422,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -348,205 +466,262 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
-    <col min="2" max="2" width="19.81640625" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" customWidth="1"/>
-    <col min="4" max="4" width="18.90625" customWidth="1"/>
-    <col min="5" max="5" width="18.7265625" customWidth="1"/>
-    <col min="6" max="6" width="19.90625" customWidth="1"/>
-    <col min="7" max="7" width="19.26953125" customWidth="1"/>
-    <col min="8" max="8" width="18.54296875" customWidth="1"/>
-    <col min="9" max="9" width="19.1796875" customWidth="1"/>
-    <col min="10" max="10" width="19.81640625" customWidth="1"/>
-    <col min="11" max="11" width="11.08984375" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="37.4140625" customWidth="1"/>
+    <col min="2" max="2" width="21.08203125" customWidth="1"/>
+    <col min="3" max="3" width="20.4140625" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="19.4140625" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="19.08203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.4140625" customWidth="1"/>
+    <col min="10" max="10" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -575,160 +750,391 @@
       <c r="J2" t="s">
         <v>21</v>
       </c>
-      <c r="K2">
-        <v>300</v>
-      </c>
-      <c r="L2">
-        <v>300</v>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" t="s">
+        <v>71</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3">
+      <c r="F18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" t="s">
+        <v>88</v>
+      </c>
+      <c r="J18" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" t="s">
         <v>32</v>
       </c>
-      <c r="L3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7">
-        <v>300</v>
-      </c>
-      <c r="L7">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8">
-        <v>32</v>
-      </c>
-      <c r="L8">
+      <c r="L18" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L18" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>